--- a/docs/点位采集表.xlsx
+++ b/docs/点位采集表.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O300"/>
+  <dimension ref="A1:Q300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -475,6 +475,8 @@
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -551,6 +553,16 @@
       <c r="O1" s="2" t="inlineStr">
         <is>
           <t>骑手原话</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>出处</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>位置说明</t>
         </is>
       </c>
     </row>
@@ -2954,8 +2966,8 @@
     <dataValidation sqref="C2:C300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉框选择" error="子类见“分类”工作表" type="list">
       <formula1>"官方驿站,友好商户,公共卫生间,充换电点,自发休息点,电动车禁入,末端步行远,停车困难,通行困难,需减速路口,难找入口"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉框选择" error="来源只能是：实地走访 / 骑手指认 / 实地走访+骑手指认" type="list">
-      <formula1>"实地走访,骑手指认,实地走访+骑手指认"</formula1>
+    <dataValidation sqref="L2:L300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉框选择" error="来源只能是：实地走访 / 骑手指认 / 实地走访+骑手指认 / 公开资料" type="list">
+      <formula1>"实地走访,骑手指认,实地走访+骑手指认,公开资料"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="坐标超出杨浦区范围" error="经度应在 121.4~121.7，纬度应在 31.2~31.4。是不是把经度纬度填反了？" type="decimal" operator="between">
       <formula1>121.4</formula1>
@@ -2976,7 +2988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3002,7 +3014,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2. 点位必须是你亲自走到、或骑手当面指认的地方，不能从网上或 AI 那里抄。</t>
+          <t>2. 点位必须是你亲自走到、或骑手当面指认的地方，不能让 AI 编。引用政府等公开资料时，来源填“公开资料”，并在“出处”列写网址。</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3306,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>实地走访 / 骑手指认 / 实地走访+骑手指认</t>
+          <t>实地走访 / 骑手指认 / 实地走访+骑手指认 / 公开资料</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -3364,6 +3376,34 @@
           <t>自己在路边就是舒服……非常应急的情况下才去。</t>
         </is>
       </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>出处</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>来源为“公开资料”时必填：网址，多个用空格分隔</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>位置说明</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>坐标不是现场取的时写明怎么定的，如“按高德地图上××大厦的位置标定”</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
